--- a/backend/model/test-bill/test_bill_english.xlsx
+++ b/backend/model/test-bill/test_bill_english.xlsx
@@ -1,93 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ใบกำกับสินค้า" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
-  <si>
-    <t>Product Code</t>
-  </si>
-  <si>
-    <t>Product Name</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>TRB-NH-5000</t>
-  </si>
-  <si>
-    <t>BKP-TOY-HILUX</t>
-  </si>
-  <si>
-    <t>FLT-FORD-8184</t>
-  </si>
-  <si>
-    <t>RAD-FORD-BRS</t>
-  </si>
-  <si>
-    <t>Turbo Assembly Ford 5000</t>
-  </si>
-  <si>
-    <t>Brake Pad Front Set Toyota Hilux</t>
-  </si>
-  <si>
-    <t>Air Filter Assembly Ford 6600</t>
-  </si>
-  <si>
-    <t>Brass Radiator Ford DT</t>
-  </si>
-  <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>set</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -99,35 +59,96 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -415,96 +436,586 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ใบนำเข้าสินค้า / PURCHASE INVOICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ชื่อบริษัท (TH)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>บริษัท เอ็มที อะไหล่ยนต์ จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ชื่อบริษัท (EN)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MT Auto Parts Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ชื่อย่อ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MT Auto Parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ที่อยู่</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>99/5 ถ.พหลโยธิน ต.คูคต อ.ลำลูกกา จ.ปทุมธานี 12130</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>เบอร์โทรฝ่ายขาย</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>02-998-4521</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Line ฝ่ายขาย</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>@mtautoparts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>อีเมลฝ่ายขาย</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sale@mtautoparts.co.th</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>เลขที่บิล</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INV-2025-08471</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>วันที่รับสินค้า</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ครบกำหนดชำระ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>เครดิต</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30 Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ขนส่งโดย</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kerry Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Net Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>TRB-ISZ-4JJ1</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Turbocharger Isuzu 4JJ1 D-Max 3.0 VGS</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H18" s="4" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>BKP-MIT-L200</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Brake Pad Front Set Mitsubishi L200 Triton</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>920</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>27100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>FLT-AIR-1KD</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Air Filter Toyota 1KD-FTV Fortuner/Hilux</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>RAD-FORD-DT</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Brass Radiator Ford 6600/7000 Tractor</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>33800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>SHK-ISZ-DMAX</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Shock Absorber Rear Isuzu D-Max 2012-2019</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BLT-TIM-2KD</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Timing Belt Kit Toyota 2KD-FTV</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>CLT-ISZ-NKR</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Clutch Kit Isuzu NKR (Cover+Disc+Bearing)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>41500</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>WP-FORD-6610</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Water Pump Ford 6610/7610 Tractor</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>20250</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C2">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ALT-TOY-VIGO</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Alternator 12V 90A Toyota Hilux Vigo 2KD</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2">
-        <v>9200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>4200</v>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>OIL-HYD-AW46</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Hydraulic Oil AW46 (20L Drum)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>drum</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>28500</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>387750</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>VAT 7%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>27142.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ยอดรวมสุทธิ</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>414892.5</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>